--- a/output/laminas_comunales/comunal_s_isapre_a_2023_magallanes.xlsx
+++ b/output/laminas_comunales/comunal_s_isapre_a_2023_magallanes.xlsx
@@ -384,67 +384,67 @@
         </is>
       </c>
       <c r="C2">
-        <v>21236</v>
+        <v>14.72666625058079</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>12401</t>
+          <t>12302</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Natales</t>
+          <t>Primavera</t>
         </is>
       </c>
       <c r="C3">
-        <v>2198</v>
+        <v>9.217391304347826</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>12301</t>
+          <t>12401</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Porvenir</t>
+          <t>Natales</t>
         </is>
       </c>
       <c r="C4">
-        <v>439</v>
+        <v>7.513759272553242</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>12201</t>
+          <t>12301</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cabo de Hornos</t>
+          <t>Porvenir</t>
         </is>
       </c>
       <c r="C5">
-        <v>55</v>
+        <v>5.863496727661279</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>12302</t>
+          <t>12201</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Primavera</t>
+          <t>Cabo de Hornos</t>
         </is>
       </c>
       <c r="C6">
-        <v>53</v>
+        <v>2.755511022044088</v>
       </c>
     </row>
   </sheetData>
@@ -500,7 +500,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a ISAPRE</t>
+          <t>Porcentaje de residentes afiliados a ISAPRE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/output/laminas_comunales/comunal_s_isapre_a_2023_magallanes.xlsx
+++ b/output/laminas_comunales/comunal_s_isapre_a_2023_magallanes.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C171"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -375,61 +375,61 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>12101</t>
+          <t>12401</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Punta Arenas</t>
+          <t>Natales</t>
         </is>
       </c>
       <c r="C2">
-        <v>14.72666625058079</v>
+        <v>86.23389054114108</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>12302</t>
+          <t>12301</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Primavera</t>
+          <t>Porvenir</t>
         </is>
       </c>
       <c r="C3">
-        <v>9.217391304347826</v>
+        <v>85.88219580606385</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>12401</t>
+          <t>12302</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Natales</t>
+          <t>Primavera</t>
         </is>
       </c>
       <c r="C4">
-        <v>7.513759272553242</v>
+        <v>81.56521739130434</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>12301</t>
+          <t>12101</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Porvenir</t>
+          <t>Punta Arenas</t>
         </is>
       </c>
       <c r="C5">
-        <v>5.863496727661279</v>
+        <v>77.83857254804059</v>
       </c>
     </row>
     <row r="6">
@@ -444,7 +444,2482 @@
         </is>
       </c>
       <c r="C6">
+        <v>74.09819639278557</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>45.91304347826087</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>44.97128355816749</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>43.24342802447612</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>42.99046251666496</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>40.91091224789636</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>40.80970312272453</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>39.27855711422846</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>37.02886942531605</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>35.65217391304348</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>35.04741552023508</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>34.81963927855711</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>32.52173913043478</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>32.38300345263734</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>31.42072523768906</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>28.82329370909576</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>28.35671342685371</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>27.30434782608696</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>27.25450901803607</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>26.69811643250265</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>25.92977857296412</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>16.52173913043478</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>15.81407773474022</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>15.31125012819198</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>15.03006012024048</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>14.77955911823647</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>14.72666625058079</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>14.13116067850942</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>13.92335828803883</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>13.61569753529553</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>13.4174272724165</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>13.27655310621243</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>13.27385225446963</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>13.22941236796226</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>13.04928542807533</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>12.75788656111955</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>12.67120200276004</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>12.52173913043478</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>12.35913759266579</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>11.90213660099445</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>11.86055830105516</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>11.82608695652174</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>11.41979431013757</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>11.24818829273029</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>10.99374423136089</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>10.96567383464672</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>10.6006221584111</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>10.44477093628957</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>10.37074148296593</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>10.26086956521739</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>10.15092827567784</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>10.05743288366502</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>10.02004008016032</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>9.847365829640571</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>9.802983335760501</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>9.739130434782609</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>9.608809925035194</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>9.217391304347826</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>9.217391304347826</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>9.217391304347826</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>9.021296960995453</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>8.617234468937875</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>8.510343201503456</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>8.128931144721603</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>8.11623246492986</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>7.513759272553242</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>7.214428857715431</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>6.21632304907733</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>5.863496727661279</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>5.739130434782608</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>5.160320641282565</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>4.467917820394489</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>4.436862435073266</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>4.420218999868239</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>3.652173913043478</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>3.512755442767463</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>3.478260869565217</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>3.2919700543534</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>3.075568130595488</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>3.045841452158753</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C88">
         <v>2.755511022044088</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>2.495128327820195</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>2.434782608695652</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>2.434782608695652</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>2.350741284893816</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>2.122037988640856</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>2.068640300691396</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>2.052690341953246</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>2.049916436085741</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>1.995825271669406</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>1.863056780501145</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>1.629491117937759</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>1.565217391304348</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>1.549352210498197</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>1.524954750660536</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>1.522874321259908</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>1.516633033058023</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>1.455856818485375</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>1.452905811623247</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>1.391304347826087</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>1.363962670495334</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>1.302605210420842</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>1.281919803097118</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>1.268245991864082</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>1.217391304347826</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>1.217391304347826</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>1.217391304347826</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>1.213550746931939</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>1.043478260869565</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>1.043478260869565</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>1.04262810651899</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>1.041805796714305</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>0.9947697672033637</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>0.9750233738480032</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>0.881527981835181</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>0.8548150126886603</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>0.8548150126886603</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>0.8517034068136272</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>0.8272655795986736</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>0.6956521739130435</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>0.6811807132362762</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>0.6734352032270194</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>0.6012024048096193</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>0.5511022044088176</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>0.5511022044088176</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>0.5476158675036731</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>0.5217391304347826</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>0.5093494684305884</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>0.5075464137838921</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>0.501002004008016</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>0.501002004008016</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>0.4941899292106318</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>0.4512357706901856</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>0.4008016032064128</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>0.3507014028056112</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>0.3006012024048096</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>0.3006012024048096</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>0.2137037531721651</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>0.2004008016032064</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>0.2004008016032064</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>0.1538303763716542</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>0.1503006012024048</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C150">
+        <v>0.1047149464982906</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>0.08204286739821556</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>0.0610259290850965</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>0.0501002004008016</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C154">
+        <v>0.04006945371978095</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>0.006836905616517964</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>0.004854335268132676</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>0.003418452808258982</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>0.001386952933752193</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
